--- a/data/processed/positivacao/2022-07_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2022-07_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25257,7 +25257,7 @@
     <row r="959">
       <c r="A959" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B959" t="inlineStr"/>
@@ -36921,7 +36921,7 @@
     <row r="1408">
       <c r="A1408" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1408" t="inlineStr"/>
@@ -65917,7 +65917,7 @@
     <row r="2524">
       <c r="A2524" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2524" t="inlineStr"/>
@@ -67588,12 +67588,12 @@
       <c r="A2589" t="inlineStr"/>
       <c r="B2589" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 27 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 59.814,21
+          <t>Vendedor 1 - VENDEDOR 01: positivou 27 cliente(s), não positivou 89 cliente(s) - Total vendido: R$ 59.814,21
 Vendedor 18 - LOJA: positivou 66 cliente(s), não positivou 767 cliente(s) - Total vendido: R$ 80.145,34
-Vendedor 3 - FERNANDA: positivou 103 cliente(s), não positivou 345 cliente(s) - Total vendido: R$ 110.432,71
-Vendedor 4 - DANIELA: positivou 38 cliente(s), não positivou 623 cliente(s) - Total vendido: R$ 23.411,17
+Vendedor 3 - VENDEDOR 03: positivou 103 cliente(s), não positivou 345 cliente(s) - Total vendido: R$ 110.432,71
+Vendedor 4 - VENDEDOR 04: positivou 38 cliente(s), não positivou 623 cliente(s) - Total vendido: R$ 23.411,17
 Vendedor 5 - SITE: positivou 10 cliente(s), não positivou 443 cliente(s) - Total vendido: R$ 982,19
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2589" t="inlineStr"/>
